--- a/healthcare_assessment_forms/015_trauma_informed_care_assessment--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/015_trauma_informed_care_assessment--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>trauma_informed_care_practice</t>
+          <t>Trauma Informed Care Practice</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>trauma_informed_care_practice_scale</t>
+          <t>awareness_and_understanding</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>trauma_informed_care_practice_scale</t>
+          <t>Awareness and Understanding</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>training_priorities</t>
+          <t>staff_engagement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>training_priorities</t>
+          <t>Staff Engagement</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>resource_planning</t>
+          <t>resources_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>resource_planning</t>
+          <t>Resources and Support</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ongoing_improvement</t>
+          <t>policies_procedures</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ongoing_improvement</t>
+          <t>Policies and Procedures</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>staff_reflections</t>
+          <t>staff_retention</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>staff_reflections</t>
+          <t>Staff Retention</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>organizational_support</t>
+          <t>evaluation_scale</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>organizational_support</t>
+          <t>Evaluation Scale</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>evaluation_comments</t>
+          <t>review_by</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>evaluation_comments</t>
+          <t>Review By</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>evaluation_scale</t>
+          <t>date_submitted</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>evaluation_scale</t>
+          <t>Date Submitted</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>date_completed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>Date Completed</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>date_reviewed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>Date Reviewed</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,292 +796,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>evaluation_comments</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>evaluation_comments</t>
+          <t>Submitted By</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>review_by</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>review_by</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>date_submitted</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>date_submitted</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date_completed</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>date_completed</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>date_reviewed</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>date_reviewed</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>review_by</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>review_by</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>date_submitted</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>date_submitted</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>date_completed</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>date_completed</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>date_reviewed</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>date_reviewed</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>date_submitted</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>date_submitted</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,187 +850,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>training_priorities_choices</t>
+          <t>awareness_and_understanding_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'a_-_high_priority',_'value':_'a'}</t>
+          <t>a_-_high_priority</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'A - High Priority', 'value': 'A'}</t>
+          <t>A - High Priority</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>training_priorities_choices</t>
+          <t>awareness_and_understanding_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'b_-_medium_priority',_'value':_'b'}</t>
+          <t>b_-_medium_priority</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'B - Medium Priority', 'value': 'B'}</t>
+          <t>B - Medium Priority</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training_priorities_choices</t>
+          <t>awareness_and_understanding_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'c_-_low_priority',_'value':_'c'}</t>
+          <t>c_-_low_priority</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'C - Low Priority', 'value': 'C'}</t>
+          <t>C - Low Priority</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>organizational_support_choices</t>
+          <t>staff_engagement_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'a_-_high',_'value':_'a'}</t>
+          <t>a_-_high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'A - High', 'value': 'A'}</t>
+          <t>A - High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organizational_support_choices</t>
+          <t>staff_engagement_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'b_-_medium',_'value':_'b'}</t>
+          <t>b_-_medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'B - Medium', 'value': 'B'}</t>
+          <t>B - Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organizational_support_choices</t>
+          <t>staff_engagement_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'c_-_low',_'value':_'c'}</t>
+          <t>c_-_low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'C - Low', 'value': 'C'}</t>
+          <t>C - Low</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organizational_support_choices</t>
+          <t>staff_engagement_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'d_-_none',_'value':_'d'}</t>
+          <t>d_-_none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'D - None', 'value': 'D'}</t>
+          <t>D - None</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>policies_procedures_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'a_-_good',_'value':_'a'}</t>
+          <t>a_-_effective</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'A - Good', 'value': 'A'}</t>
+          <t>A - Effective</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>policies_procedures_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'b_-_fair',_'value':_'b'}</t>
+          <t>b_-_partially_effective</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'B - Fair', 'value': 'B'}</t>
+          <t>B - Partially Effective</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>policies_procedures_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'c_-_poor',_'value':_'c'}</t>
+          <t>c_-_not_at_all</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'C - Poor', 'value': 'C'}</t>
+          <t>C - Not at All</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>staff_retention_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'d_-_not_at_all',_'value':_'d'}</t>
+          <t>a_-_increase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'D - Not at All', 'value': 'D'}</t>
+          <t>A - Increase</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>staff_retention_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>b_-_maintain</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B - Maintain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>staff_retention_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>c_-_decrease</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C - Decrease</t>
         </is>
       </c>
     </row>
